--- a/UConnBleedBlue/wwwroot/Data/Donations.xlsx
+++ b/UConnBleedBlue/wwwroot/Data/Donations.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\EXT\J4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\EXT\TA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C352400-684C-4055-B260-1EAD24BDAABA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{669E900E-37EB-4213-BD95-8890B4F6EA7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-15" yWindow="-525" windowWidth="21390" windowHeight="13635" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="76">
   <si>
     <t>bbfg-foundation-inc-_donations_2024-10-06-09-53-29-0400</t>
   </si>
@@ -530,6 +530,12 @@
   </si>
   <si>
     <t>Ryan Timko</t>
+  </si>
+  <si>
+    <t>Pisciottano</t>
+  </si>
+  <si>
+    <t>Jim Pisciottano</t>
   </si>
 </sst>
 </file>
@@ -1806,7 +1812,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr defaultColWidth="8.28515625" defaultRowHeight="20.100000000000001" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="16.85546875" style="1" customWidth="1"/>
@@ -1866,25 +1872,25 @@
     </row>
     <row r="3" spans="1:9" ht="44.1" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="D3" s="5">
-        <v>5.52</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>19</v>
+        <v>104.42</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>29</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G3" s="5">
-        <v>8603107141</v>
+        <v>2404014479</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>11</v>
@@ -1895,57 +1901,51 @@
     </row>
     <row r="4" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>23</v>
+        <v>59</v>
       </c>
       <c r="D4" s="5">
-        <v>104.42</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>24</v>
-      </c>
+        <v>260.58999999999997</v>
+      </c>
+      <c r="E4" s="6"/>
       <c r="F4" s="4" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="G4" s="5">
-        <v>4134413609</v>
+        <v>8606256805</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>10</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="I4" s="6"/>
     </row>
     <row r="5" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>26</v>
+        <v>61</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>27</v>
+        <v>62</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>28</v>
+        <v>63</v>
       </c>
       <c r="D5" s="5">
         <v>104.42</v>
       </c>
-      <c r="E5" s="4" t="s">
-        <v>29</v>
-      </c>
+      <c r="E5" s="6"/>
       <c r="F5" s="4" t="s">
-        <v>30</v>
+        <v>64</v>
       </c>
       <c r="G5" s="5">
-        <v>2404014479</v>
+        <v>2032576982</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>11</v>
+        <v>52</v>
       </c>
       <c r="I5" s="4" t="s">
         <v>10</v>
@@ -1953,25 +1953,25 @@
     </row>
     <row r="6" spans="1:9" ht="68.099999999999994" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="D6" s="5">
-        <v>104.42</v>
+        <v>5.52</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="G6" s="5">
-        <v>6132945300</v>
+        <v>8603107141</v>
       </c>
       <c r="H6" s="4" t="s">
         <v>11</v>
@@ -1982,25 +1982,25 @@
     </row>
     <row r="7" spans="1:9" ht="68.099999999999994" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="D7" s="5">
         <v>260.58999999999997</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="G7" s="5">
-        <v>3606491781</v>
+        <v>8603107141</v>
       </c>
       <c r="H7" s="4" t="s">
         <v>11</v>
@@ -2011,138 +2011,124 @@
     </row>
     <row r="8" spans="1:9" ht="68.099999999999994" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>41</v>
+        <v>69</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="D8" s="5">
         <v>104.42</v>
       </c>
-      <c r="E8" s="7" t="s">
-        <v>44</v>
-      </c>
+      <c r="E8" s="6"/>
       <c r="F8" s="4" t="s">
-        <v>45</v>
+        <v>72</v>
       </c>
       <c r="G8" s="5">
-        <v>6785162269</v>
+        <v>5085611474</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>11</v>
+        <v>52</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="68.099999999999994" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D9" s="5">
-        <v>260.58999999999997</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>46</v>
-      </c>
+        <v>520.87</v>
+      </c>
+      <c r="E9" s="6"/>
       <c r="F9" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G9" s="5">
-        <v>8603107141</v>
+        <v>7323066786</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>11</v>
+        <v>52</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="20.100000000000001" customHeight="1">
+    <row r="10" spans="1:9" ht="68.099999999999994" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>50</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="C10" s="4"/>
       <c r="D10" s="5">
-        <v>104.39</v>
+        <v>52.37</v>
       </c>
       <c r="E10" s="6"/>
-      <c r="F10" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="G10" s="5">
-        <v>6178755735</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="I10" s="6"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
     </row>
     <row r="11" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>14</v>
+        <v>49</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="D11" s="5">
-        <v>520.87</v>
+        <v>104.39</v>
       </c>
       <c r="E11" s="6"/>
       <c r="F11" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G11" s="5">
-        <v>7323066786</v>
+        <v>6178755735</v>
       </c>
       <c r="H11" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="I11" s="4" t="s">
-        <v>12</v>
-      </c>
+      <c r="I11" s="6"/>
     </row>
     <row r="12" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="D12" s="5">
-        <v>156.47999999999999</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>73</v>
+        <v>104.42</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>44</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="G12" s="5">
-        <v>3867482571</v>
+        <v>6785162269</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>52</v>
+        <v>11</v>
       </c>
       <c r="I12" s="4" t="s">
         <v>10</v>
@@ -2150,51 +2136,55 @@
     </row>
     <row r="13" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="D13" s="5">
-        <v>260.58999999999997</v>
+        <v>250</v>
       </c>
       <c r="E13" s="6"/>
       <c r="F13" s="4" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="G13" s="5">
-        <v>8606256805</v>
+        <v>6037709880</v>
       </c>
       <c r="H13" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="I13" s="6"/>
+      <c r="I13" s="4" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="14" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="D14" s="5">
-        <v>104.42</v>
-      </c>
-      <c r="E14" s="6"/>
+        <v>260.58999999999997</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>39</v>
+      </c>
       <c r="F14" s="4" t="s">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="G14" s="5">
-        <v>2032576982</v>
+        <v>3606491781</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>52</v>
+        <v>11</v>
       </c>
       <c r="I14" s="4" t="s">
         <v>10</v>
@@ -2202,23 +2192,25 @@
     </row>
     <row r="15" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A15" s="3" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="D15" s="5">
-        <v>250</v>
-      </c>
-      <c r="E15" s="6"/>
+        <v>156.47999999999999</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>73</v>
+      </c>
       <c r="F15" s="4" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="G15" s="5">
-        <v>6037709880</v>
+        <v>3867482571</v>
       </c>
       <c r="H15" s="4" t="s">
         <v>52</v>
@@ -2229,56 +2221,90 @@
     </row>
     <row r="16" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>69</v>
+        <v>21</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>70</v>
+        <v>22</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>71</v>
+        <v>23</v>
       </c>
       <c r="D16" s="5">
         <v>104.42</v>
       </c>
-      <c r="E16" s="6"/>
+      <c r="E16" s="4" t="s">
+        <v>24</v>
+      </c>
       <c r="F16" s="4" t="s">
-        <v>72</v>
+        <v>25</v>
       </c>
       <c r="G16" s="5">
-        <v>5085611474</v>
+        <v>4134413609</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>52</v>
+        <v>11</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="20.100000000000001" customHeight="1">
+      <c r="A17" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D17" s="5">
+        <v>104.42</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G17" s="5">
+        <v>6132945300</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I17">
+    <sortCondition ref="B7:B17"/>
+  </sortState>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="C3" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000049010000}"/>
-    <hyperlink ref="E3" r:id="rId2" display="kpdemers073@gmail.com" xr:uid="{00000000-0004-0000-0000-00004A010000}"/>
-    <hyperlink ref="C4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-00004B010000}"/>
-    <hyperlink ref="E4" r:id="rId4" display="Ralphtiner83@gmail.com" xr:uid="{00000000-0004-0000-0000-00004C010000}"/>
-    <hyperlink ref="C5" r:id="rId5" xr:uid="{00000000-0004-0000-0000-00004E010000}"/>
-    <hyperlink ref="C6" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000053010000}"/>
-    <hyperlink ref="E6" r:id="rId7" display="jason.derek.ward@uconn.edu" xr:uid="{00000000-0004-0000-0000-000054010000}"/>
-    <hyperlink ref="C7" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000055010000}"/>
-    <hyperlink ref="E7" r:id="rId9" display="kpdemers073@gmail.com" xr:uid="{00000000-0004-0000-0000-000056010000}"/>
-    <hyperlink ref="C8" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000058010000}"/>
-    <hyperlink ref="E8" r:id="rId11" display="tkramsey29@gmail.com" xr:uid="{00000000-0004-0000-0000-000059010000}"/>
-    <hyperlink ref="C9" r:id="rId12" xr:uid="{00000000-0004-0000-0000-000061010000}"/>
-    <hyperlink ref="E9" r:id="rId13" display="kpdemers073@gmail.com" xr:uid="{00000000-0004-0000-0000-000062010000}"/>
-    <hyperlink ref="C10" r:id="rId14" xr:uid="{00000000-0004-0000-0000-000066010000}"/>
-    <hyperlink ref="C11" r:id="rId15" xr:uid="{00000000-0004-0000-0000-000067010000}"/>
-    <hyperlink ref="C12" r:id="rId16" xr:uid="{00000000-0004-0000-0000-000068010000}"/>
-    <hyperlink ref="C13" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000069010000}"/>
-    <hyperlink ref="C14" r:id="rId18" xr:uid="{00000000-0004-0000-0000-00006B010000}"/>
-    <hyperlink ref="C15" r:id="rId19" xr:uid="{00000000-0004-0000-0000-00006E010000}"/>
-    <hyperlink ref="C16" r:id="rId20" xr:uid="{00000000-0004-0000-0000-00006F010000}"/>
+    <hyperlink ref="C6" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000049010000}"/>
+    <hyperlink ref="E6" r:id="rId2" display="kpdemers073@gmail.com" xr:uid="{00000000-0004-0000-0000-00004A010000}"/>
+    <hyperlink ref="C16" r:id="rId3" xr:uid="{00000000-0004-0000-0000-00004B010000}"/>
+    <hyperlink ref="E16" r:id="rId4" display="Ralphtiner83@gmail.com" xr:uid="{00000000-0004-0000-0000-00004C010000}"/>
+    <hyperlink ref="C3" r:id="rId5" xr:uid="{00000000-0004-0000-0000-00004E010000}"/>
+    <hyperlink ref="C17" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000053010000}"/>
+    <hyperlink ref="E17" r:id="rId7" display="jason.derek.ward@uconn.edu" xr:uid="{00000000-0004-0000-0000-000054010000}"/>
+    <hyperlink ref="C14" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000055010000}"/>
+    <hyperlink ref="E14" r:id="rId9" display="kpdemers073@gmail.com" xr:uid="{00000000-0004-0000-0000-000056010000}"/>
+    <hyperlink ref="C12" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000058010000}"/>
+    <hyperlink ref="E12" r:id="rId11" display="tkramsey29@gmail.com" xr:uid="{00000000-0004-0000-0000-000059010000}"/>
+    <hyperlink ref="C7" r:id="rId12" xr:uid="{00000000-0004-0000-0000-000061010000}"/>
+    <hyperlink ref="E7" r:id="rId13" display="kpdemers073@gmail.com" xr:uid="{00000000-0004-0000-0000-000062010000}"/>
+    <hyperlink ref="C11" r:id="rId14" xr:uid="{00000000-0004-0000-0000-000066010000}"/>
+    <hyperlink ref="C9" r:id="rId15" xr:uid="{00000000-0004-0000-0000-000067010000}"/>
+    <hyperlink ref="C15" r:id="rId16" xr:uid="{00000000-0004-0000-0000-000068010000}"/>
+    <hyperlink ref="C4" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000069010000}"/>
+    <hyperlink ref="C5" r:id="rId18" xr:uid="{00000000-0004-0000-0000-00006B010000}"/>
+    <hyperlink ref="C13" r:id="rId19" xr:uid="{00000000-0004-0000-0000-00006E010000}"/>
+    <hyperlink ref="C8" r:id="rId20" xr:uid="{00000000-0004-0000-0000-00006F010000}"/>
   </hyperlinks>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
   <pageSetup orientation="portrait"/>

--- a/UConnBleedBlue/wwwroot/Data/Donations.xlsx
+++ b/UConnBleedBlue/wwwroot/Data/Donations.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\EXT\TA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\EXT\RY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{669E900E-37EB-4213-BD95-8890B4F6EA7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DC7C1EB-B27C-46C7-AAB8-0EC959BF6042}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-15" yWindow="-525" windowWidth="21390" windowHeight="13635" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,17 +20,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="76">
-  <si>
-    <t>bbfg-foundation-inc-_donations_2024-10-06-09-53-29-0400</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="102">
+  <si>
+    <t>bbfg-foundation-inc-_donations_2024-10-09-22-03-31-0400</t>
   </si>
   <si>
     <t>Name</t>
   </si>
   <si>
-    <t>Donor Last Name</t>
-  </si>
-  <si>
     <t>Donor Email</t>
   </si>
   <si>
@@ -55,6 +52,9 @@
     <t>Help UConn achieve athletic success</t>
   </si>
   <si>
+    <t>Support the philanthropic efforts of UConn student-athletes</t>
+  </si>
+  <si>
     <t>Football</t>
   </si>
   <si>
@@ -64,9 +64,6 @@
     <t>Patrick Margiatto</t>
   </si>
   <si>
-    <t>Margiatto</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <u/>
@@ -80,9 +77,6 @@
   </si>
   <si>
     <t>Kenneth Demers</t>
-  </si>
-  <si>
-    <t>Demers</t>
   </si>
   <si>
     <r>
@@ -125,9 +119,6 @@
     <t>Ralph Tiner</t>
   </si>
   <si>
-    <t>Tiner</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <u/>
@@ -167,9 +158,6 @@
     <t>Al Akowitz</t>
   </si>
   <si>
-    <t>Akowitz</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <u/>
@@ -189,9 +177,6 @@
   </si>
   <si>
     <t>Leah Ward</t>
-  </si>
-  <si>
-    <t>Ward</t>
   </si>
   <si>
     <r>
@@ -262,9 +247,6 @@
     <t>Thomas Szarzynski</t>
   </si>
   <si>
-    <t>Szarzynski</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <u/>
@@ -315,9 +297,6 @@
     <t>Terrence Ramsey</t>
   </si>
   <si>
-    <t>Ramsey</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <u/>
@@ -403,139 +382,292 @@
     <t>Craig Primiani</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Helvetica Neue"/>
+        <family val="2"/>
+      </rPr>
+      <t>craigprimiani@aol.com</t>
+    </r>
+  </si>
+  <si>
+    <t>10/02/2024 18:24:16</t>
+  </si>
+  <si>
+    <t>Football Alumni Tailgate</t>
+  </si>
+  <si>
+    <t>10/03/2024 00:57:54</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Helvetica Neue"/>
+        <family val="2"/>
+      </rPr>
+      <t>ryantimko@hotmail.com</t>
+    </r>
+  </si>
+  <si>
+    <t>10/03/2024 11:43:56</t>
+  </si>
+  <si>
+    <t>Patrick Anglim</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Helvetica Neue"/>
+        <family val="2"/>
+      </rPr>
+      <t>patrick@drpflexpak.com</t>
+    </r>
+  </si>
+  <si>
+    <t>10/03/2024 13:43:22</t>
+  </si>
+  <si>
+    <t>Drew Bickel</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Helvetica Neue"/>
+        <family val="2"/>
+      </rPr>
+      <t>bickeldrew@gmail.com</t>
+    </r>
+  </si>
+  <si>
+    <t>10/04/2024 15:43:59</t>
+  </si>
+  <si>
+    <t>Joseph Simeone</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Helvetica Neue"/>
+        <family val="2"/>
+      </rPr>
+      <t>jksimeone@comcast.net</t>
+    </r>
+  </si>
+  <si>
+    <t>10/05/2024 11:22:09</t>
+  </si>
+  <si>
+    <t>Steve Dixon</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Helvetica Neue"/>
+        <family val="2"/>
+      </rPr>
+      <t>sddixon46@gmail.com</t>
+    </r>
+  </si>
+  <si>
+    <t>10/05/2024 11:24:52</t>
+  </si>
+  <si>
+    <t>Steven Smith</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Helvetica Neue"/>
+        <family val="2"/>
+      </rPr>
+      <t>steven_j_smith1@hotmail.com</t>
+    </r>
+  </si>
+  <si>
+    <t>10/07/2024 11:30:14</t>
+  </si>
+  <si>
+    <t>Robin and Stu Milberg</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Helvetica Neue"/>
+        <family val="2"/>
+      </rPr>
+      <t>stuart.milberg@yahoo.com</t>
+    </r>
+  </si>
+  <si>
+    <t>10/07/2024 14:54:22</t>
+  </si>
+  <si>
+    <t>James Sproul</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Helvetica Neue"/>
+        <family val="2"/>
+      </rPr>
+      <t>jsproul@sproulco.com</t>
+    </r>
+  </si>
+  <si>
+    <t>10/09/2024 09:46:23</t>
+  </si>
+  <si>
+    <t>Steven Flig</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Helvetica Neue"/>
+        <family val="2"/>
+      </rPr>
+      <t>sflig1@gmail.com</t>
+    </r>
+  </si>
+  <si>
+    <t>My pleasure to donate to Andy’s tailgate fund. Andy was my freshman coach in the fall of 1968.Remember it like it was yesterday.</t>
+  </si>
+  <si>
+    <t>10/09/2024 10:12:23</t>
+  </si>
+  <si>
+    <t>Martha Worley</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Helvetica Neue"/>
+        <family val="2"/>
+      </rPr>
+      <t>martha529@aol.com</t>
+    </r>
+  </si>
+  <si>
+    <t>10/09/2024 13:43:07</t>
+  </si>
+  <si>
+    <t>John Billingslea</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Helvetica Neue"/>
+        <family val="2"/>
+      </rPr>
+      <t>rembeau@aol.com</t>
+    </r>
+  </si>
+  <si>
+    <t>10/09/2024 16:26:41</t>
+  </si>
+  <si>
+    <t>Last Name</t>
+  </si>
+  <si>
+    <t>Akowitz</t>
+  </si>
+  <si>
+    <t>Bickel</t>
+  </si>
+  <si>
     <t>Primiani</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Helvetica Neue"/>
-        <family val="2"/>
-      </rPr>
-      <t>craigprimiani@aol.com</t>
-    </r>
-  </si>
-  <si>
-    <t>10/02/2024 18:24:16</t>
-  </si>
-  <si>
-    <t>Football Alumni Tailgate</t>
-  </si>
-  <si>
-    <t>10/03/2024 00:57:54</t>
+    <t>Sproul</t>
+  </si>
+  <si>
+    <t>Demers</t>
+  </si>
+  <si>
+    <t>Ward</t>
+  </si>
+  <si>
+    <t>Anglim</t>
+  </si>
+  <si>
+    <t>Margiatto</t>
+  </si>
+  <si>
+    <t>Tiner</t>
+  </si>
+  <si>
+    <t>Billingslea</t>
+  </si>
+  <si>
+    <t>Dixon</t>
+  </si>
+  <si>
+    <t>Flig</t>
+  </si>
+  <si>
+    <t>Smith</t>
+  </si>
+  <si>
+    <t>Szarzynski</t>
+  </si>
+  <si>
+    <t>Ramsey</t>
+  </si>
+  <si>
+    <t>Simeone</t>
+  </si>
+  <si>
+    <t>Worley</t>
   </si>
   <si>
     <t>Timko</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Helvetica Neue"/>
-        <family val="2"/>
-      </rPr>
-      <t>ryantimko@hotmail.com</t>
-    </r>
-  </si>
-  <si>
-    <t>10/03/2024 11:43:56</t>
-  </si>
-  <si>
-    <t>Patrick Anglim</t>
-  </si>
-  <si>
-    <t>Anglim</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Helvetica Neue"/>
-        <family val="2"/>
-      </rPr>
-      <t>patrick@drpflexpak.com</t>
-    </r>
-  </si>
-  <si>
-    <t>10/03/2024 13:43:22</t>
-  </si>
-  <si>
-    <t>Drew Bickel</t>
-  </si>
-  <si>
-    <t>Bickel</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Helvetica Neue"/>
-        <family val="2"/>
-      </rPr>
-      <t>bickeldrew@gmail.com</t>
-    </r>
-  </si>
-  <si>
-    <t>10/04/2024 15:43:59</t>
-  </si>
-  <si>
-    <t>Joseph Simeone</t>
-  </si>
-  <si>
-    <t>Simeone</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Helvetica Neue"/>
-        <family val="2"/>
-      </rPr>
-      <t>jksimeone@comcast.net</t>
-    </r>
-  </si>
-  <si>
-    <t>10/05/2024 11:22:09</t>
-  </si>
-  <si>
-    <t>Steve Dixon</t>
-  </si>
-  <si>
-    <t>Dixon</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Helvetica Neue"/>
-        <family val="2"/>
-      </rPr>
-      <t>sddixon46@gmail.com</t>
-    </r>
-  </si>
-  <si>
-    <t>10/05/2024 11:24:52</t>
-  </si>
-  <si>
     <t>Ryan Timko</t>
   </si>
   <si>
+    <t>Milberg</t>
+  </si>
+  <si>
+    <t>Nancy Pisciottano</t>
+  </si>
+  <si>
     <t>Pisciottano</t>
-  </si>
-  <si>
-    <t>Jim Pisciottano</t>
   </si>
 </sst>
 </file>
@@ -575,7 +707,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -594,8 +726,14 @@
         <bgColor auto="1"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -648,13 +786,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="10"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="10"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="10"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -679,8 +830,14 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1812,14 +1969,14 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr defaultColWidth="8.28515625" defaultRowHeight="20.100000000000001" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="16.85546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15.28515625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="27" style="1" customWidth="1"/>
+    <col min="1" max="1" width="33" style="1" customWidth="1"/>
+    <col min="2" max="2" width="23.85546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="31.7109375" style="1" customWidth="1"/>
     <col min="4" max="4" width="8.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="58.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="86.42578125" style="1" customWidth="1"/>
     <col min="6" max="6" width="17" style="1" customWidth="1"/>
     <col min="7" max="7" width="12.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="24" style="1" customWidth="1"/>
@@ -1829,65 +1986,65 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
-      <c r="I1" s="8"/>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
     </row>
     <row r="2" spans="1:9" ht="20.25" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>8</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="44.1" customHeight="1">
       <c r="A3" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" s="5">
+        <v>1104.42</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>26</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D3" s="5">
-        <v>104.42</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>30</v>
       </c>
       <c r="G3" s="5">
         <v>2404014479</v>
@@ -1896,108 +2053,106 @@
         <v>11</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>58</v>
+        <v>48</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>86</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="D4" s="5">
         <v>260.58999999999997</v>
       </c>
       <c r="E4" s="6"/>
       <c r="F4" s="4" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="G4" s="5">
         <v>8606256805</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="I4" s="6"/>
     </row>
     <row r="5" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>62</v>
+        <v>51</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>81</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="D5" s="5">
         <v>104.42</v>
       </c>
       <c r="E5" s="6"/>
       <c r="F5" s="4" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="G5" s="5">
         <v>2032576982</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="68.099999999999994" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>17</v>
+        <v>76</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>89</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>18</v>
+        <v>77</v>
       </c>
       <c r="D6" s="5">
-        <v>5.52</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>19</v>
-      </c>
+        <v>208.54</v>
+      </c>
+      <c r="E6" s="6"/>
       <c r="F6" s="4" t="s">
-        <v>20</v>
+        <v>78</v>
       </c>
       <c r="G6" s="5">
-        <v>8603107141</v>
+        <v>8189035486</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="68.099999999999994" customHeight="1">
       <c r="A7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="D7" s="5">
+        <v>5.52</v>
+      </c>
+      <c r="E7" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="F7" s="4" t="s">
         <v>18</v>
-      </c>
-      <c r="D7" s="5">
-        <v>260.58999999999997</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>47</v>
       </c>
       <c r="G7" s="5">
         <v>8603107141</v>
@@ -2006,305 +2161,469 @@
         <v>11</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="68.099999999999994" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>70</v>
+        <v>15</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>84</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>71</v>
+        <v>16</v>
       </c>
       <c r="D8" s="5">
-        <v>104.42</v>
-      </c>
-      <c r="E8" s="6"/>
+        <v>260.58999999999997</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>39</v>
+      </c>
       <c r="F8" s="4" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="G8" s="5">
-        <v>5085611474</v>
+        <v>8603107141</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>52</v>
+        <v>11</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="68.099999999999994" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>14</v>
+        <v>57</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>90</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>15</v>
+        <v>58</v>
       </c>
       <c r="D9" s="5">
-        <v>520.87</v>
+        <v>104.42</v>
       </c>
       <c r="E9" s="6"/>
       <c r="F9" s="4" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="G9" s="5">
-        <v>7323066786</v>
+        <v>5085611474</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="I9" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="68.099999999999994" customHeight="1">
+    <row r="10" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C10" s="4"/>
+        <v>69</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>70</v>
+      </c>
       <c r="D10" s="5">
-        <v>52.37</v>
-      </c>
-      <c r="E10" s="6"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="4"/>
+        <v>260.58999999999997</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="G10" s="5">
+        <v>4045937655</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="11" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>49</v>
+        <v>13</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>87</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="D11" s="5">
-        <v>104.39</v>
+        <v>520.87</v>
       </c>
       <c r="E11" s="6"/>
       <c r="F11" s="4" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="G11" s="5">
-        <v>6178755735</v>
+        <v>7323066786</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="I11" s="6"/>
+        <v>44</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="12" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>42</v>
+        <v>63</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>99</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="D12" s="5">
-        <v>104.42</v>
-      </c>
-      <c r="E12" s="7" t="s">
+        <v>520.87</v>
+      </c>
+      <c r="E12" s="6"/>
+      <c r="F12" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="G12" s="5">
+        <v>2034510452</v>
+      </c>
+      <c r="H12" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="F12" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="G12" s="5">
-        <v>6785162269</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="I12" s="4" t="s">
-        <v>10</v>
-      </c>
+      <c r="I12" s="6"/>
     </row>
     <row r="13" spans="1:9" ht="20.100000000000001" customHeight="1">
-      <c r="A13" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>67</v>
-      </c>
+      <c r="A13" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="C13" s="4"/>
       <c r="D13" s="5">
-        <v>250</v>
+        <v>52.37</v>
       </c>
       <c r="E13" s="6"/>
-      <c r="F13" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="G13" s="5">
-        <v>6037709880</v>
-      </c>
-      <c r="H13" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="I13" s="4" t="s">
-        <v>10</v>
-      </c>
+      <c r="F13" s="4"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="6"/>
     </row>
     <row r="14" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>37</v>
+        <v>41</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>82</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D14" s="5">
-        <v>260.58999999999997</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>39</v>
-      </c>
+        <v>104.39</v>
+      </c>
+      <c r="E14" s="6"/>
       <c r="F14" s="4" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G14" s="5">
-        <v>3606491781</v>
+        <v>6178755735</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="I14" s="4" t="s">
-        <v>10</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="I14" s="6"/>
     </row>
     <row r="15" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A15" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>54</v>
+        <v>35</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>94</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="D15" s="5">
-        <v>156.47999999999999</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>73</v>
+        <v>104.42</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>37</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="G15" s="5">
-        <v>3867482571</v>
+        <v>6785162269</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>52</v>
+        <v>11</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>22</v>
+        <v>54</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>95</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="D16" s="5">
-        <v>104.42</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>24</v>
-      </c>
+        <v>250</v>
+      </c>
+      <c r="E16" s="6"/>
       <c r="F16" s="4" t="s">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="G16" s="5">
-        <v>4134413609</v>
+        <v>6037709880</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A17" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D17" s="5">
+        <v>260.58999999999997</v>
+      </c>
+      <c r="E17" s="6"/>
+      <c r="F17" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G17" s="5">
+        <v>8604550270</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="I17" s="6"/>
+    </row>
+    <row r="18" spans="1:9" ht="20.100000000000001" customHeight="1">
+      <c r="A18" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="D18" s="5">
+        <v>104.42</v>
+      </c>
+      <c r="E18" s="6"/>
+      <c r="F18" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="G18" s="5">
+        <v>6174592969</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="20.100000000000001" customHeight="1">
+      <c r="A19" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B19" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="C19" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="D19" s="5">
+        <v>260.58999999999997</v>
+      </c>
+      <c r="E19" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="D17" s="5">
+      <c r="F19" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G19" s="5">
+        <v>3606491781</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="20.100000000000001" customHeight="1">
+      <c r="A20" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D20" s="5">
+        <v>156.47999999999999</v>
+      </c>
+      <c r="E20" s="6"/>
+      <c r="F20" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="G20" s="5">
+        <v>3867482571</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="I20" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="20.100000000000001" customHeight="1">
+      <c r="A21" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D21" s="5">
         <v>104.42</v>
       </c>
-      <c r="E17" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="G17" s="5">
+      <c r="E21" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G21" s="5">
+        <v>4134413609</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I21" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="20.100000000000001" customHeight="1">
+      <c r="A22" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D22" s="5">
+        <v>104.42</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G22" s="5">
         <v>6132945300</v>
       </c>
-      <c r="H17" s="4" t="s">
+      <c r="H22" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="I17" s="4" t="s">
-        <v>10</v>
+      <c r="I22" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="20.100000000000001" customHeight="1">
+      <c r="A23" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="D23" s="5">
+        <v>100</v>
+      </c>
+      <c r="E23" s="6"/>
+      <c r="F23" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="G23" s="6"/>
+      <c r="H23" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="I23" s="4" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I17">
-    <sortCondition ref="B7:B17"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I23">
+    <sortCondition ref="B7:B23"/>
   </sortState>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="C6" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000049010000}"/>
-    <hyperlink ref="E6" r:id="rId2" display="kpdemers073@gmail.com" xr:uid="{00000000-0004-0000-0000-00004A010000}"/>
-    <hyperlink ref="C16" r:id="rId3" xr:uid="{00000000-0004-0000-0000-00004B010000}"/>
-    <hyperlink ref="E16" r:id="rId4" display="Ralphtiner83@gmail.com" xr:uid="{00000000-0004-0000-0000-00004C010000}"/>
-    <hyperlink ref="C3" r:id="rId5" xr:uid="{00000000-0004-0000-0000-00004E010000}"/>
-    <hyperlink ref="C17" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000053010000}"/>
-    <hyperlink ref="E17" r:id="rId7" display="jason.derek.ward@uconn.edu" xr:uid="{00000000-0004-0000-0000-000054010000}"/>
-    <hyperlink ref="C14" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000055010000}"/>
-    <hyperlink ref="E14" r:id="rId9" display="kpdemers073@gmail.com" xr:uid="{00000000-0004-0000-0000-000056010000}"/>
-    <hyperlink ref="C12" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000058010000}"/>
-    <hyperlink ref="E12" r:id="rId11" display="tkramsey29@gmail.com" xr:uid="{00000000-0004-0000-0000-000059010000}"/>
-    <hyperlink ref="C7" r:id="rId12" xr:uid="{00000000-0004-0000-0000-000061010000}"/>
-    <hyperlink ref="E7" r:id="rId13" display="kpdemers073@gmail.com" xr:uid="{00000000-0004-0000-0000-000062010000}"/>
-    <hyperlink ref="C11" r:id="rId14" xr:uid="{00000000-0004-0000-0000-000066010000}"/>
-    <hyperlink ref="C9" r:id="rId15" xr:uid="{00000000-0004-0000-0000-000067010000}"/>
-    <hyperlink ref="C15" r:id="rId16" xr:uid="{00000000-0004-0000-0000-000068010000}"/>
-    <hyperlink ref="C4" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000069010000}"/>
-    <hyperlink ref="C5" r:id="rId18" xr:uid="{00000000-0004-0000-0000-00006B010000}"/>
-    <hyperlink ref="C13" r:id="rId19" xr:uid="{00000000-0004-0000-0000-00006E010000}"/>
-    <hyperlink ref="C8" r:id="rId20" xr:uid="{00000000-0004-0000-0000-00006F010000}"/>
+    <hyperlink ref="C21" r:id="rId1" xr:uid="{00000000-0004-0000-0000-00004B010000}"/>
+    <hyperlink ref="E21" r:id="rId2" display="Ralphtiner83@gmail.com" xr:uid="{00000000-0004-0000-0000-00004C010000}"/>
+    <hyperlink ref="C3" r:id="rId3" xr:uid="{00000000-0004-0000-0000-00004E010000}"/>
+    <hyperlink ref="C22" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000053010000}"/>
+    <hyperlink ref="E22" r:id="rId5" display="jason.derek.ward@uconn.edu" xr:uid="{00000000-0004-0000-0000-000054010000}"/>
+    <hyperlink ref="C19" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000055010000}"/>
+    <hyperlink ref="E19" r:id="rId7" display="kpdemers073@gmail.com" xr:uid="{00000000-0004-0000-0000-000056010000}"/>
+    <hyperlink ref="C15" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000058010000}"/>
+    <hyperlink ref="E15" r:id="rId9" display="tkramsey29@gmail.com" xr:uid="{00000000-0004-0000-0000-000059010000}"/>
+    <hyperlink ref="C8" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000061010000}"/>
+    <hyperlink ref="E8" r:id="rId11" display="kpdemers073@gmail.com" xr:uid="{00000000-0004-0000-0000-000062010000}"/>
+    <hyperlink ref="C14" r:id="rId12" xr:uid="{00000000-0004-0000-0000-000066010000}"/>
+    <hyperlink ref="C11" r:id="rId13" xr:uid="{00000000-0004-0000-0000-000067010000}"/>
+    <hyperlink ref="C20" r:id="rId14" xr:uid="{00000000-0004-0000-0000-000068010000}"/>
+    <hyperlink ref="C4" r:id="rId15" xr:uid="{00000000-0004-0000-0000-000069010000}"/>
+    <hyperlink ref="C5" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00006B010000}"/>
+    <hyperlink ref="C16" r:id="rId17" xr:uid="{00000000-0004-0000-0000-00006E010000}"/>
+    <hyperlink ref="C9" r:id="rId18" xr:uid="{00000000-0004-0000-0000-00006F010000}"/>
+    <hyperlink ref="C17" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000072010000}"/>
+    <hyperlink ref="C12" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000075010000}"/>
+    <hyperlink ref="C18" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000079010000}"/>
+    <hyperlink ref="C10" r:id="rId22" xr:uid="{00000000-0004-0000-0000-00007B010000}"/>
+    <hyperlink ref="C23" r:id="rId23" xr:uid="{00000000-0004-0000-0000-00007E010000}"/>
+    <hyperlink ref="C6" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000080010000}"/>
+    <hyperlink ref="E7" r:id="rId25" display="kpdemers073@gmail.com" xr:uid="{00000000-0004-0000-0000-00004A010000}"/>
+    <hyperlink ref="C7" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000049010000}"/>
   </hyperlinks>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
   <pageSetup orientation="portrait"/>

--- a/UConnBleedBlue/wwwroot/Data/Donations.xlsx
+++ b/UConnBleedBlue/wwwroot/Data/Donations.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\EXT\RY\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\EXT\CH\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DC7C1EB-B27C-46C7-AAB8-0EC959BF6042}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{880FB449-7B54-4074-82A4-AD7068AA123E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-15" yWindow="-525" windowWidth="21390" windowHeight="13635" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-15" yWindow="-555" windowWidth="21390" windowHeight="13665" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1 - bbfg-foundation-inc-_" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="106">
   <si>
     <t>bbfg-foundation-inc-_donations_2024-10-09-22-03-31-0400</t>
   </si>
@@ -668,13 +668,25 @@
   </si>
   <si>
     <t>Pisciottano</t>
+  </si>
+  <si>
+    <t>Christopher Spelman</t>
+  </si>
+  <si>
+    <t>Spelman</t>
+  </si>
+  <si>
+    <t>Glenn Marrus</t>
+  </si>
+  <si>
+    <t>Marrus</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <color indexed="8"/>
@@ -705,6 +717,17 @@
       <color indexed="8"/>
       <name val="Helvetica Neue"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color indexed="8"/>
+      <name val="Helvetica Neue"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Helvetica Neue"/>
     </font>
   </fonts>
   <fills count="5">
@@ -805,7 +828,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -833,11 +856,17 @@
     <xf numFmtId="49" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1969,7 +1998,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr defaultColWidth="8.28515625" defaultRowHeight="20.100000000000001" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="33" style="1" customWidth="1"/>
@@ -1986,17 +2015,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
     </row>
     <row r="2" spans="1:9" ht="20.25" customHeight="1">
       <c r="A2" s="2" t="s">
@@ -2278,122 +2307,112 @@
     </row>
     <row r="12" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>63</v>
+        <v>104</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>64</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="C12" s="4"/>
       <c r="D12" s="5">
-        <v>520.87</v>
+        <v>52.37</v>
       </c>
       <c r="E12" s="6"/>
-      <c r="F12" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="G12" s="5">
-        <v>2034510452</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="I12" s="6"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
     </row>
     <row r="13" spans="1:9" ht="20.100000000000001" customHeight="1">
-      <c r="A13" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="B13" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="C13" s="4"/>
+      <c r="A13" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>64</v>
+      </c>
       <c r="D13" s="5">
-        <v>52.37</v>
+        <v>520.87</v>
       </c>
       <c r="E13" s="6"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="4"/>
+      <c r="F13" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="G13" s="5">
+        <v>2034510452</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>44</v>
+      </c>
       <c r="I13" s="6"/>
     </row>
     <row r="14" spans="1:9" ht="20.100000000000001" customHeight="1">
-      <c r="A14" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>42</v>
-      </c>
+      <c r="A14" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="C14" s="4"/>
       <c r="D14" s="5">
-        <v>104.39</v>
+        <v>52.37</v>
       </c>
       <c r="E14" s="6"/>
-      <c r="F14" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="G14" s="5">
-        <v>6178755735</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>44</v>
-      </c>
+      <c r="F14" s="4"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="4"/>
       <c r="I14" s="6"/>
     </row>
     <row r="15" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A15" s="3" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D15" s="5">
-        <v>104.42</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>37</v>
-      </c>
+        <v>104.39</v>
+      </c>
+      <c r="E15" s="6"/>
       <c r="F15" s="4" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="G15" s="5">
-        <v>6785162269</v>
+        <v>6178755735</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="I15" s="4" t="s">
-        <v>9</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="I15" s="6"/>
     </row>
     <row r="16" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="D16" s="5">
-        <v>250</v>
-      </c>
-      <c r="E16" s="6"/>
+        <v>104.42</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>37</v>
+      </c>
       <c r="F16" s="4" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="G16" s="5">
-        <v>6037709880</v>
+        <v>6785162269</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="I16" s="4" t="s">
         <v>9</v>
@@ -2401,133 +2420,121 @@
     </row>
     <row r="17" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A17" s="3" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D17" s="5">
-        <v>260.58999999999997</v>
+        <v>250</v>
       </c>
       <c r="E17" s="6"/>
       <c r="F17" s="4" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="G17" s="5">
-        <v>8604550270</v>
+        <v>6037709880</v>
       </c>
       <c r="H17" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="I17" s="6"/>
+      <c r="I17" s="4" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="18" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D18" s="5">
-        <v>104.42</v>
+        <v>260.58999999999997</v>
       </c>
       <c r="E18" s="6"/>
       <c r="F18" s="4" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="G18" s="5">
-        <v>6174592969</v>
+        <v>8604550270</v>
       </c>
       <c r="H18" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="I18" s="4" t="s">
-        <v>10</v>
-      </c>
+      <c r="I18" s="6"/>
     </row>
     <row r="19" spans="1:9" ht="20.100000000000001" customHeight="1">
-      <c r="A19" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>32</v>
-      </c>
+      <c r="A19" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="C19" s="4"/>
       <c r="D19" s="5">
-        <v>260.58999999999997</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="G19" s="5">
-        <v>3606491781</v>
-      </c>
-      <c r="H19" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="I19" s="4" t="s">
-        <v>9</v>
-      </c>
+        <v>104.42</v>
+      </c>
+      <c r="E19" s="6"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="6"/>
     </row>
     <row r="20" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>98</v>
+        <v>66</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="D20" s="5">
-        <v>156.47999999999999</v>
+        <v>104.42</v>
       </c>
       <c r="E20" s="6"/>
       <c r="F20" s="4" t="s">
-        <v>47</v>
+        <v>68</v>
       </c>
       <c r="G20" s="5">
-        <v>3867482571</v>
+        <v>6174592969</v>
       </c>
       <c r="H20" s="4" t="s">
         <v>44</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="D21" s="5">
-        <v>104.42</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>21</v>
+        <v>260.58999999999997</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>33</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="G21" s="5">
-        <v>4134413609</v>
+        <v>3606491781</v>
       </c>
       <c r="H21" s="4" t="s">
         <v>11</v>
@@ -2538,28 +2545,26 @@
     </row>
     <row r="22" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>27</v>
+        <v>98</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="D22" s="5">
-        <v>104.42</v>
-      </c>
-      <c r="E22" s="7" t="s">
-        <v>29</v>
-      </c>
+        <v>156.47999999999999</v>
+      </c>
+      <c r="E22" s="6"/>
       <c r="F22" s="4" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="G22" s="5">
-        <v>6132945300</v>
+        <v>3867482571</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="I22" s="4" t="s">
         <v>9</v>
@@ -2567,66 +2572,124 @@
     </row>
     <row r="23" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>73</v>
+        <v>19</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>74</v>
+        <v>20</v>
       </c>
       <c r="D23" s="5">
-        <v>100</v>
-      </c>
-      <c r="E23" s="6"/>
+        <v>104.42</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>21</v>
+      </c>
       <c r="F23" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="G23" s="6"/>
+        <v>22</v>
+      </c>
+      <c r="G23" s="5">
+        <v>4134413609</v>
+      </c>
       <c r="H23" s="4" t="s">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="I23" s="4" t="s">
         <v>9</v>
       </c>
     </row>
+    <row r="24" spans="1:9" ht="20.100000000000001" customHeight="1">
+      <c r="A24" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D24" s="5">
+        <v>104.42</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G24" s="5">
+        <v>6132945300</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I24" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="20.100000000000001" customHeight="1">
+      <c r="A25" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="D25" s="5">
+        <v>100</v>
+      </c>
+      <c r="E25" s="6"/>
+      <c r="F25" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="G25" s="6"/>
+      <c r="H25" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="I25" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I23">
-    <sortCondition ref="B7:B23"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I25">
+    <sortCondition ref="B7:B25"/>
   </sortState>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="C21" r:id="rId1" xr:uid="{00000000-0004-0000-0000-00004B010000}"/>
-    <hyperlink ref="E21" r:id="rId2" display="Ralphtiner83@gmail.com" xr:uid="{00000000-0004-0000-0000-00004C010000}"/>
+    <hyperlink ref="C23" r:id="rId1" xr:uid="{00000000-0004-0000-0000-00004B010000}"/>
+    <hyperlink ref="E23" r:id="rId2" display="Ralphtiner83@gmail.com" xr:uid="{00000000-0004-0000-0000-00004C010000}"/>
     <hyperlink ref="C3" r:id="rId3" xr:uid="{00000000-0004-0000-0000-00004E010000}"/>
-    <hyperlink ref="C22" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000053010000}"/>
-    <hyperlink ref="E22" r:id="rId5" display="jason.derek.ward@uconn.edu" xr:uid="{00000000-0004-0000-0000-000054010000}"/>
-    <hyperlink ref="C19" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000055010000}"/>
-    <hyperlink ref="E19" r:id="rId7" display="kpdemers073@gmail.com" xr:uid="{00000000-0004-0000-0000-000056010000}"/>
-    <hyperlink ref="C15" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000058010000}"/>
-    <hyperlink ref="E15" r:id="rId9" display="tkramsey29@gmail.com" xr:uid="{00000000-0004-0000-0000-000059010000}"/>
+    <hyperlink ref="C24" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000053010000}"/>
+    <hyperlink ref="E24" r:id="rId5" display="jason.derek.ward@uconn.edu" xr:uid="{00000000-0004-0000-0000-000054010000}"/>
+    <hyperlink ref="C21" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000055010000}"/>
+    <hyperlink ref="E21" r:id="rId7" display="kpdemers073@gmail.com" xr:uid="{00000000-0004-0000-0000-000056010000}"/>
+    <hyperlink ref="C16" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000058010000}"/>
+    <hyperlink ref="E16" r:id="rId9" display="tkramsey29@gmail.com" xr:uid="{00000000-0004-0000-0000-000059010000}"/>
     <hyperlink ref="C8" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000061010000}"/>
     <hyperlink ref="E8" r:id="rId11" display="kpdemers073@gmail.com" xr:uid="{00000000-0004-0000-0000-000062010000}"/>
-    <hyperlink ref="C14" r:id="rId12" xr:uid="{00000000-0004-0000-0000-000066010000}"/>
+    <hyperlink ref="C15" r:id="rId12" xr:uid="{00000000-0004-0000-0000-000066010000}"/>
     <hyperlink ref="C11" r:id="rId13" xr:uid="{00000000-0004-0000-0000-000067010000}"/>
-    <hyperlink ref="C20" r:id="rId14" xr:uid="{00000000-0004-0000-0000-000068010000}"/>
+    <hyperlink ref="C22" r:id="rId14" xr:uid="{00000000-0004-0000-0000-000068010000}"/>
     <hyperlink ref="C4" r:id="rId15" xr:uid="{00000000-0004-0000-0000-000069010000}"/>
     <hyperlink ref="C5" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00006B010000}"/>
-    <hyperlink ref="C16" r:id="rId17" xr:uid="{00000000-0004-0000-0000-00006E010000}"/>
+    <hyperlink ref="C17" r:id="rId17" xr:uid="{00000000-0004-0000-0000-00006E010000}"/>
     <hyperlink ref="C9" r:id="rId18" xr:uid="{00000000-0004-0000-0000-00006F010000}"/>
-    <hyperlink ref="C17" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000072010000}"/>
-    <hyperlink ref="C12" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000075010000}"/>
-    <hyperlink ref="C18" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000079010000}"/>
+    <hyperlink ref="C18" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000072010000}"/>
+    <hyperlink ref="C13" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000075010000}"/>
+    <hyperlink ref="C20" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000079010000}"/>
     <hyperlink ref="C10" r:id="rId22" xr:uid="{00000000-0004-0000-0000-00007B010000}"/>
-    <hyperlink ref="C23" r:id="rId23" xr:uid="{00000000-0004-0000-0000-00007E010000}"/>
+    <hyperlink ref="C25" r:id="rId23" xr:uid="{00000000-0004-0000-0000-00007E010000}"/>
     <hyperlink ref="C6" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000080010000}"/>
     <hyperlink ref="E7" r:id="rId25" display="kpdemers073@gmail.com" xr:uid="{00000000-0004-0000-0000-00004A010000}"/>
     <hyperlink ref="C7" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000049010000}"/>
   </hyperlinks>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
-  <pageSetup orientation="portrait"/>
+  <pageSetup orientation="portrait" r:id="rId27"/>
   <headerFooter>
     <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
   </headerFooter>

--- a/UConnBleedBlue/wwwroot/Data/Donations.xlsx
+++ b/UConnBleedBlue/wwwroot/Data/Donations.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\EXT\CH\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos\UConnBleedBlue\UConnBleedBlue\wwwroot\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{880FB449-7B54-4074-82A4-AD7068AA123E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4DF9A51-9764-4151-BA4E-324470F79B2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-15" yWindow="-555" windowWidth="21390" windowHeight="13665" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3675" yWindow="1800" windowWidth="21600" windowHeight="13680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1 - bbfg-foundation-inc-_" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="110">
   <si>
     <t>bbfg-foundation-inc-_donations_2024-10-09-22-03-31-0400</t>
   </si>
@@ -680,13 +680,25 @@
   </si>
   <si>
     <t>Marrus</t>
+  </si>
+  <si>
+    <t>Pastor Andre McGuire</t>
+  </si>
+  <si>
+    <t>McGuire</t>
+  </si>
+  <si>
+    <t>Clifford Demers</t>
+  </si>
+  <si>
+    <t>cordseller1@gmail.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="10"/>
       <color indexed="8"/>
@@ -727,6 +739,12 @@
     <font>
       <b/>
       <sz val="10"/>
+      <name val="Helvetica Neue"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="10"/>
       <name val="Helvetica Neue"/>
     </font>
   </fonts>
@@ -823,12 +841,15 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -862,14 +883,27 @@
     <xf numFmtId="49" fontId="5" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="49" fontId="7" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1995,16 +2029,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr>
+  <sheetPr codeName="Sheet1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr defaultColWidth="8.28515625" defaultRowHeight="20.100000000000001" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="33" style="1" customWidth="1"/>
     <col min="2" max="2" width="23.85546875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="31.7109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="8.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="39.7109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="8.42578125" style="16" customWidth="1"/>
     <col min="5" max="5" width="86.42578125" style="1" customWidth="1"/>
     <col min="6" max="6" width="17" style="1" customWidth="1"/>
     <col min="7" max="7" width="12.7109375" style="1" customWidth="1"/>
@@ -2015,17 +2049,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="27.75" customHeight="1">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="11"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
+      <c r="I1" s="12"/>
     </row>
     <row r="2" spans="1:9" ht="20.25" customHeight="1">
       <c r="A2" s="2" t="s">
@@ -2037,7 +2071,7 @@
       <c r="C2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="14" t="s">
         <v>3</v>
       </c>
       <c r="E2" s="2" t="s">
@@ -2066,7 +2100,7 @@
       <c r="C3" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D3" s="5">
+      <c r="D3" s="15">
         <v>1104.42</v>
       </c>
       <c r="E3" s="4" t="s">
@@ -2095,7 +2129,7 @@
       <c r="C4" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="15">
         <v>260.58999999999997</v>
       </c>
       <c r="E4" s="6"/>
@@ -2120,7 +2154,7 @@
       <c r="C5" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="15">
         <v>104.42</v>
       </c>
       <c r="E5" s="6"/>
@@ -2147,7 +2181,7 @@
       <c r="C6" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D6" s="15">
         <v>208.54</v>
       </c>
       <c r="E6" s="6"/>
@@ -2166,32 +2200,22 @@
     </row>
     <row r="7" spans="1:9" ht="68.099999999999994" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="B7" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="5">
-        <v>5.52</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G7" s="5">
-        <v>8603107141</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>9</v>
-      </c>
+      <c r="C7" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="D7" s="15">
+        <v>50</v>
+      </c>
+      <c r="E7" s="6"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
     </row>
     <row r="8" spans="1:9" ht="68.099999999999994" customHeight="1">
       <c r="A8" s="3" t="s">
@@ -2203,14 +2227,14 @@
       <c r="C8" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="5">
-        <v>260.58999999999997</v>
+      <c r="D8" s="15">
+        <v>5.52</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="G8" s="5">
         <v>8603107141</v>
@@ -2224,165 +2248,169 @@
     </row>
     <row r="9" spans="1:9" ht="68.099999999999994" customHeight="1">
       <c r="A9" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="15">
+        <v>260.58999999999997</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G9" s="5">
+        <v>8603107141</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="68.099999999999994" customHeight="1">
+      <c r="A10" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B10" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C10" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="D9" s="5">
+      <c r="D10" s="15">
         <v>104.42</v>
       </c>
-      <c r="E9" s="6"/>
-      <c r="F9" s="4" t="s">
+      <c r="E10" s="6"/>
+      <c r="F10" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="G9" s="5">
+      <c r="G10" s="5">
         <v>5085611474</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="20.100000000000001" customHeight="1">
-      <c r="A10" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="D10" s="5">
-        <v>260.58999999999997</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="G10" s="5">
-        <v>4045937655</v>
       </c>
       <c r="H10" s="4" t="s">
         <v>44</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>13</v>
+        <v>69</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D11" s="5">
-        <v>520.87</v>
-      </c>
-      <c r="E11" s="6"/>
+        <v>70</v>
+      </c>
+      <c r="D11" s="15">
+        <v>260.58999999999997</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>71</v>
+      </c>
       <c r="F11" s="4" t="s">
-        <v>45</v>
+        <v>72</v>
       </c>
       <c r="G11" s="5">
-        <v>7323066786</v>
+        <v>4045937655</v>
       </c>
       <c r="H11" s="4" t="s">
         <v>44</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>104</v>
+        <v>13</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="C12" s="4"/>
-      <c r="D12" s="5">
-        <v>52.37</v>
+        <v>87</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12" s="15">
+        <v>520.87</v>
       </c>
       <c r="E12" s="6"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="4"/>
-      <c r="I12" s="4"/>
+      <c r="F12" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="G12" s="5">
+        <v>7323066786</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="13" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>63</v>
+        <v>104</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="D13" s="5">
-        <v>520.87</v>
+        <v>105</v>
+      </c>
+      <c r="C13" s="4"/>
+      <c r="D13" s="15">
+        <v>52.37</v>
       </c>
       <c r="E13" s="6"/>
-      <c r="F13" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="G13" s="5">
-        <v>2034510452</v>
-      </c>
-      <c r="H13" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="I13" s="6"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
     </row>
     <row r="14" spans="1:9" ht="20.100000000000001" customHeight="1">
-      <c r="A14" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>101</v>
+      <c r="A14" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>107</v>
       </c>
       <c r="C14" s="4"/>
-      <c r="D14" s="5">
-        <v>52.37</v>
+      <c r="D14" s="15">
+        <v>104.42</v>
       </c>
       <c r="E14" s="6"/>
       <c r="F14" s="4"/>
       <c r="G14" s="5"/>
       <c r="H14" s="4"/>
-      <c r="I14" s="6"/>
+      <c r="I14" s="4"/>
     </row>
     <row r="15" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A15" s="3" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D15" s="5">
-        <v>104.39</v>
+        <v>64</v>
+      </c>
+      <c r="D15" s="15">
+        <v>520.87</v>
       </c>
       <c r="E15" s="6"/>
       <c r="F15" s="4" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="G15" s="5">
-        <v>6178755735</v>
+        <v>2034510452</v>
       </c>
       <c r="H15" s="4" t="s">
         <v>44</v>
@@ -2390,207 +2418,193 @@
       <c r="I15" s="6"/>
     </row>
     <row r="16" spans="1:9" ht="20.100000000000001" customHeight="1">
-      <c r="A16" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D16" s="5">
-        <v>104.42</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="G16" s="5">
-        <v>6785162269</v>
-      </c>
-      <c r="H16" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="I16" s="4" t="s">
-        <v>9</v>
-      </c>
+      <c r="A16" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="C16" s="4"/>
+      <c r="D16" s="15">
+        <v>52.37</v>
+      </c>
+      <c r="E16" s="6"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="6"/>
     </row>
     <row r="17" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A17" s="3" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D17" s="5">
-        <v>250</v>
+        <v>42</v>
+      </c>
+      <c r="D17" s="15">
+        <v>104.39</v>
       </c>
       <c r="E17" s="6"/>
       <c r="F17" s="4" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="G17" s="5">
-        <v>6037709880</v>
+        <v>6178755735</v>
       </c>
       <c r="H17" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="I17" s="4" t="s">
-        <v>9</v>
-      </c>
+      <c r="I17" s="6"/>
     </row>
     <row r="18" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="D18" s="5">
-        <v>260.58999999999997</v>
-      </c>
-      <c r="E18" s="6"/>
+        <v>36</v>
+      </c>
+      <c r="D18" s="15">
+        <v>104.42</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>37</v>
+      </c>
       <c r="F18" s="4" t="s">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="G18" s="5">
-        <v>8604550270</v>
+        <v>6785162269</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="I18" s="6"/>
+        <v>11</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="19" spans="1:9" ht="20.100000000000001" customHeight="1">
-      <c r="A19" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="B19" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="C19" s="4"/>
-      <c r="D19" s="5">
-        <v>104.42</v>
+      <c r="A19" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D19" s="15">
+        <v>250</v>
       </c>
       <c r="E19" s="6"/>
-      <c r="F19" s="4"/>
-      <c r="G19" s="5"/>
-      <c r="H19" s="4"/>
-      <c r="I19" s="6"/>
+      <c r="F19" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="G19" s="5">
+        <v>6037709880</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="20" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="D20" s="5">
-        <v>104.42</v>
+        <v>61</v>
+      </c>
+      <c r="D20" s="15">
+        <v>260.58999999999997</v>
       </c>
       <c r="E20" s="6"/>
       <c r="F20" s="4" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="G20" s="5">
-        <v>6174592969</v>
+        <v>8604550270</v>
       </c>
       <c r="H20" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="I20" s="4" t="s">
-        <v>10</v>
-      </c>
+      <c r="I20" s="6"/>
     </row>
     <row r="21" spans="1:9" ht="20.100000000000001" customHeight="1">
-      <c r="A21" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B21" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D21" s="5">
-        <v>260.58999999999997</v>
-      </c>
-      <c r="E21" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="G21" s="5">
-        <v>3606491781</v>
-      </c>
-      <c r="H21" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="I21" s="4" t="s">
-        <v>9</v>
-      </c>
+      <c r="A21" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="C21" s="4"/>
+      <c r="D21" s="15">
+        <v>104.42</v>
+      </c>
+      <c r="E21" s="6"/>
+      <c r="F21" s="4"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="4"/>
+      <c r="I21" s="6"/>
     </row>
     <row r="22" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>98</v>
+        <v>66</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D22" s="5">
-        <v>156.47999999999999</v>
+        <v>67</v>
+      </c>
+      <c r="D22" s="15">
+        <v>104.42</v>
       </c>
       <c r="E22" s="6"/>
       <c r="F22" s="4" t="s">
-        <v>47</v>
+        <v>68</v>
       </c>
       <c r="G22" s="5">
-        <v>3867482571</v>
+        <v>6174592969</v>
       </c>
       <c r="H22" s="4" t="s">
         <v>44</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D23" s="5">
-        <v>104.42</v>
-      </c>
-      <c r="E23" s="4" t="s">
-        <v>21</v>
+        <v>32</v>
+      </c>
+      <c r="D23" s="15">
+        <v>260.58999999999997</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>33</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="G23" s="5">
-        <v>4134413609</v>
+        <v>3606491781</v>
       </c>
       <c r="H23" s="4" t="s">
         <v>11</v>
@@ -2601,28 +2615,26 @@
     </row>
     <row r="24" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>27</v>
+        <v>98</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D24" s="5">
-        <v>104.42</v>
-      </c>
-      <c r="E24" s="7" t="s">
-        <v>29</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="D24" s="15">
+        <v>156.47999999999999</v>
+      </c>
+      <c r="E24" s="6"/>
       <c r="F24" s="4" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="G24" s="5">
-        <v>6132945300</v>
+        <v>3867482571</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="I24" s="4" t="s">
         <v>9</v>
@@ -2630,66 +2642,126 @@
     </row>
     <row r="25" spans="1:9" ht="20.100000000000001" customHeight="1">
       <c r="A25" s="3" t="s">
-        <v>73</v>
+        <v>19</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="D25" s="5">
-        <v>100</v>
-      </c>
-      <c r="E25" s="6"/>
+        <v>20</v>
+      </c>
+      <c r="D25" s="15">
+        <v>104.42</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>21</v>
+      </c>
       <c r="F25" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="G25" s="6"/>
+        <v>22</v>
+      </c>
+      <c r="G25" s="5">
+        <v>4134413609</v>
+      </c>
       <c r="H25" s="4" t="s">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="I25" s="4" t="s">
         <v>9</v>
       </c>
     </row>
+    <row r="26" spans="1:9" ht="20.100000000000001" customHeight="1">
+      <c r="A26" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D26" s="15">
+        <v>104.42</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G26" s="5">
+        <v>6132945300</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I26" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="20.100000000000001" customHeight="1">
+      <c r="A27" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="D27" s="15">
+        <v>100</v>
+      </c>
+      <c r="E27" s="6"/>
+      <c r="F27" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="G27" s="6"/>
+      <c r="H27" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="I27" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I25">
-    <sortCondition ref="B7:B25"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:I27">
+    <sortCondition ref="B8:B27"/>
   </sortState>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="C23" r:id="rId1" xr:uid="{00000000-0004-0000-0000-00004B010000}"/>
-    <hyperlink ref="E23" r:id="rId2" display="Ralphtiner83@gmail.com" xr:uid="{00000000-0004-0000-0000-00004C010000}"/>
+    <hyperlink ref="C25" r:id="rId1" xr:uid="{00000000-0004-0000-0000-00004B010000}"/>
+    <hyperlink ref="E25" r:id="rId2" display="Ralphtiner83@gmail.com" xr:uid="{00000000-0004-0000-0000-00004C010000}"/>
     <hyperlink ref="C3" r:id="rId3" xr:uid="{00000000-0004-0000-0000-00004E010000}"/>
-    <hyperlink ref="C24" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000053010000}"/>
-    <hyperlink ref="E24" r:id="rId5" display="jason.derek.ward@uconn.edu" xr:uid="{00000000-0004-0000-0000-000054010000}"/>
-    <hyperlink ref="C21" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000055010000}"/>
-    <hyperlink ref="E21" r:id="rId7" display="kpdemers073@gmail.com" xr:uid="{00000000-0004-0000-0000-000056010000}"/>
-    <hyperlink ref="C16" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000058010000}"/>
-    <hyperlink ref="E16" r:id="rId9" display="tkramsey29@gmail.com" xr:uid="{00000000-0004-0000-0000-000059010000}"/>
-    <hyperlink ref="C8" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000061010000}"/>
-    <hyperlink ref="E8" r:id="rId11" display="kpdemers073@gmail.com" xr:uid="{00000000-0004-0000-0000-000062010000}"/>
-    <hyperlink ref="C15" r:id="rId12" xr:uid="{00000000-0004-0000-0000-000066010000}"/>
-    <hyperlink ref="C11" r:id="rId13" xr:uid="{00000000-0004-0000-0000-000067010000}"/>
-    <hyperlink ref="C22" r:id="rId14" xr:uid="{00000000-0004-0000-0000-000068010000}"/>
+    <hyperlink ref="C26" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000053010000}"/>
+    <hyperlink ref="E26" r:id="rId5" display="jason.derek.ward@uconn.edu" xr:uid="{00000000-0004-0000-0000-000054010000}"/>
+    <hyperlink ref="C23" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000055010000}"/>
+    <hyperlink ref="E23" r:id="rId7" display="kpdemers073@gmail.com" xr:uid="{00000000-0004-0000-0000-000056010000}"/>
+    <hyperlink ref="C18" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000058010000}"/>
+    <hyperlink ref="E18" r:id="rId9" display="tkramsey29@gmail.com" xr:uid="{00000000-0004-0000-0000-000059010000}"/>
+    <hyperlink ref="C9" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000061010000}"/>
+    <hyperlink ref="E9" r:id="rId11" display="kpdemers073@gmail.com" xr:uid="{00000000-0004-0000-0000-000062010000}"/>
+    <hyperlink ref="C17" r:id="rId12" xr:uid="{00000000-0004-0000-0000-000066010000}"/>
+    <hyperlink ref="C12" r:id="rId13" xr:uid="{00000000-0004-0000-0000-000067010000}"/>
+    <hyperlink ref="C24" r:id="rId14" xr:uid="{00000000-0004-0000-0000-000068010000}"/>
     <hyperlink ref="C4" r:id="rId15" xr:uid="{00000000-0004-0000-0000-000069010000}"/>
     <hyperlink ref="C5" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00006B010000}"/>
-    <hyperlink ref="C17" r:id="rId17" xr:uid="{00000000-0004-0000-0000-00006E010000}"/>
-    <hyperlink ref="C9" r:id="rId18" xr:uid="{00000000-0004-0000-0000-00006F010000}"/>
-    <hyperlink ref="C18" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000072010000}"/>
-    <hyperlink ref="C13" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000075010000}"/>
-    <hyperlink ref="C20" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000079010000}"/>
-    <hyperlink ref="C10" r:id="rId22" xr:uid="{00000000-0004-0000-0000-00007B010000}"/>
-    <hyperlink ref="C25" r:id="rId23" xr:uid="{00000000-0004-0000-0000-00007E010000}"/>
-    <hyperlink ref="C6" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000080010000}"/>
-    <hyperlink ref="E7" r:id="rId25" display="kpdemers073@gmail.com" xr:uid="{00000000-0004-0000-0000-00004A010000}"/>
-    <hyperlink ref="C7" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000049010000}"/>
+    <hyperlink ref="C19" r:id="rId17" xr:uid="{00000000-0004-0000-0000-00006E010000}"/>
+    <hyperlink ref="C10" r:id="rId18" xr:uid="{00000000-0004-0000-0000-00006F010000}"/>
+    <hyperlink ref="C20" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000072010000}"/>
+    <hyperlink ref="C22" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000079010000}"/>
+    <hyperlink ref="C11" r:id="rId21" xr:uid="{00000000-0004-0000-0000-00007B010000}"/>
+    <hyperlink ref="C27" r:id="rId22" xr:uid="{00000000-0004-0000-0000-00007E010000}"/>
+    <hyperlink ref="C6" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000080010000}"/>
+    <hyperlink ref="E8" r:id="rId24" display="kpdemers073@gmail.com" xr:uid="{00000000-0004-0000-0000-00004A010000}"/>
+    <hyperlink ref="C8" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000049010000}"/>
+    <hyperlink ref="C15" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000075010000}"/>
+    <hyperlink ref="B7" r:id="rId27" display="cordseller1@gmail.com" xr:uid="{D4876737-4A82-425C-BFF6-77E123DE6BDA}"/>
+    <hyperlink ref="C7" r:id="rId28" xr:uid="{3DE7DA4E-96FD-41FB-A669-7874992CFC34}"/>
   </hyperlinks>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
-  <pageSetup orientation="portrait" r:id="rId27"/>
+  <pageSetup orientation="portrait" r:id="rId29"/>
   <headerFooter>
     <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
   </headerFooter>

--- a/UConnBleedBlue/wwwroot/Data/Donations.xlsx
+++ b/UConnBleedBlue/wwwroot/Data/Donations.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\EXT\UT\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\EXT\KP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87AB3C03-6F99-4DB6-80F9-EC4E3CDC22C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{767EBC7C-5D9B-47FF-A329-A8C5DB1F883F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-15" yWindow="-555" windowWidth="21390" windowHeight="13665" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="85">
   <si>
     <t>Name</t>
   </si>
@@ -643,6 +643,27 @@
       </rPr>
       <t>harrison.newman98@comcast.net</t>
     </r>
+  </si>
+  <si>
+    <t>Carmen Ammirato</t>
+  </si>
+  <si>
+    <t>huskyvino@me.com</t>
+  </si>
+  <si>
+    <t>Cash</t>
+  </si>
+  <si>
+    <t>Tony Casarella</t>
+  </si>
+  <si>
+    <t>elizabeth.casarella@gmail.com</t>
+  </si>
+  <si>
+    <t>Matt Hogan</t>
+  </si>
+  <si>
+    <t>hogan6523@yahoo.com</t>
   </si>
 </sst>
 </file>
@@ -781,7 +802,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -830,6 +851,12 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1049,7 +1076,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:Z29"/>
+  <dimension ref="A1:Z32"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="21.85546875" customWidth="1"/>
@@ -1777,6 +1804,45 @@
       </c>
       <c r="H29" s="18" t="s">
         <v>54</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A30" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="B30" t="s">
+        <v>79</v>
+      </c>
+      <c r="C30" s="20">
+        <v>100</v>
+      </c>
+      <c r="D30" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A31" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="B31" t="s">
+        <v>82</v>
+      </c>
+      <c r="C31" s="20">
+        <v>100</v>
+      </c>
+      <c r="D31" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A32" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="B32" t="s">
+        <v>84</v>
+      </c>
+      <c r="C32" s="20">
+        <v>104.42</v>
       </c>
     </row>
   </sheetData>
